--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>59771.17</v>
+        <v>61507.31</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>39694.17</v>
+        <v>40847.14</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>36619.68</v>
+        <v>36764.06</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>31993.75</v>
+        <v>32521.06</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>20272.95</v>
+        <v>20607.08</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>32917.22</v>
+        <v>33459.75</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>54476.77</v>
+        <v>54610.8</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>23789.71</v>
+        <v>23848.25</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>36619.68</v>
+        <v>36148.24</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>36619.68</v>
+        <v>36148.24</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>43905.43</v>
+        <v>43340.19</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>35594.33</v>
+        <v>35136.09</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>25707.41</v>
+        <v>25376.45</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>41289.58</v>
+        <v>40758.02</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23529.45</v>
+        <v>23363.4</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>48318.64</v>
+        <v>47977.65</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>18882.44</v>
+        <v>18749.18</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>24520.46</v>
+        <v>24347.42</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10759.72</v>
+        <v>10683.79</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>24052.33</v>
+        <v>23882.59</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>102600.5</v>
+        <v>104460.72</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>13503.68</v>
+        <v>13748.51</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41294.85</v>
+        <v>42043.55</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>33990.91</v>
+        <v>34607.19</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12766</v>
+        <v>12965.98</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>20822.21</v>
+        <v>20821.14</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>37769.48</v>
+        <v>37802.01</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>38184.46</v>
+        <v>38217.35</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>38513.09</v>
+        <v>38546.27</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>62277.37</v>
+        <v>62331.02</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>19782.54</v>
+        <v>19799.58</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27675.77</v>
+        <v>27790.1</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>45793.07</v>
+        <v>45666.75</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>25993.05</v>
+        <v>25921.35</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>35594.33</v>
+        <v>35183.42</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>38269.33</v>
+        <v>37827.53</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>26813.45</v>
+        <v>26503.91</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>26789.77</v>
+        <v>26390.2</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>76642.48</v>
+        <v>75499.33</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>38513.08</v>
+        <v>37938.64</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>53414.91</v>
+        <v>52618.21</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>24520.46</v>
+        <v>24379.61</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>75876.05</v>
+        <v>75440.2</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>24592.73</v>
+        <v>24451.47</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>22290.84</v>
+        <v>22194.81</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>17644.15</v>
+        <v>17568.13</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>24052.33</v>
+        <v>23948.71</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>30549.71</v>
+        <v>30107.74</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>36488.9</v>
+        <v>35961.01</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>38478.13</v>
+        <v>37921.46</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>23076.81</v>
+        <v>22580.31</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>43907.35</v>
+        <v>42962.68</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>42586.07</v>
+        <v>41669.84</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>25295.04</v>
+        <v>24750.82</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>67563.55</v>
+        <v>66109.92</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>21335.18</v>
+        <v>20838.73</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>31642.18</v>
+        <v>30905.89</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>13652.08</v>
+        <v>13334.4</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>27685.67</v>
+        <v>27041.45</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>22710.59</v>
+        <v>22182.13</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>52413.84</v>
+        <v>51194.22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Región ;Metropolitana</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,17 +1459,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Compras GORE Maule</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2026.xlsx
@@ -562,7 +562,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1793,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1984,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2049,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2114,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2179,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2244,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2370,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2435,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2500,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2565,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2630,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2695,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2760,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2825,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2890,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3016,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3081,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3207,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3272,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3337,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3402,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3467,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3532,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3597,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3662,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3788,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3853,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3918,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3983,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4109,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4174,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4300,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4365,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4430,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
